--- a/Analysis/Prompt_Ablation/prompt_ablation_summary_by_decision_type.xlsx
+++ b/Analysis/Prompt_Ablation/prompt_ablation_summary_by_decision_type.xlsx
@@ -470,10 +470,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.02138827876976179</v>
+        <v>0.01133385667406853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3446153846153846</v>
+        <v>0.3369230769230769</v>
       </c>
     </row>
     <row r="3">
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-0.03395626246719456</v>
+        <v>-0.06311788068315549</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3085714285714286</v>
+        <v>0.3014285714285714</v>
       </c>
     </row>
     <row r="4">
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.4763299316185546</v>
+        <v>0.4844696709361382</v>
       </c>
       <c r="F4" t="n">
-        <v>0.55</v>
+        <v>0.5649999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.3614950026465752</v>
+        <v>0.3496736805337111</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6461538461538462</v>
+        <v>0.6425269645608629</v>
       </c>
     </row>
     <row r="9">
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>-0.1207200352563497</v>
+        <v>-0.1178088996583242</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2228571428571429</v>
+        <v>0.2314285714285714</v>
       </c>
     </row>
     <row r="10">
@@ -694,10 +694,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.2199495470166127</v>
+        <v>0.240030896016325</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>0.5233333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>-0.1374358974358975</v>
+        <v>-0.1486143379339142</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2646153846153846</v>
+        <v>0.2769230769230769</v>
       </c>
     </row>
     <row r="15">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.1338679037313348</v>
+        <v>0.1399612755650536</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3714285714285714</v>
+        <v>0.3757142857142857</v>
       </c>
     </row>
     <row r="16">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.2096632649518879</v>
+        <v>0.1678591267774902</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4066666666666667</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="17">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-0.1281015174210937</v>
+        <v>-0.1461020407618289</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2369230769230769</v>
+        <v>0.2338461538461538</v>
       </c>
     </row>
     <row r="21">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.06298413292322347</v>
+        <v>0.02958770037436749</v>
       </c>
       <c r="F21" t="n">
-        <v>0.332378223495702</v>
+        <v>0.3175965665236051</v>
       </c>
     </row>
     <row r="22">
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.4141581623797197</v>
+        <v>0.4464674031262856</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5433333333333333</v>
+        <v>0.5716666666666667</v>
       </c>
     </row>
     <row r="23">
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-0.1406536757453616</v>
+        <v>-0.1470779937686126</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1857585139318886</v>
+        <v>0.1851851851851852</v>
       </c>
     </row>
     <row r="27">
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-0.03763650866193553</v>
+        <v>-0.006907822152024003</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2997032640949555</v>
+        <v>0.3161764705882353</v>
       </c>
     </row>
     <row r="28">
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.02531534695789217</v>
+        <v>-0.0006226115126125598</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3833333333333334</v>
+        <v>0.3666666666666666</v>
       </c>
     </row>
     <row r="29">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.1846188166078016</v>
+        <v>0.1576265944969524</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4953846153846154</v>
+        <v>0.4738461538461539</v>
       </c>
     </row>
     <row r="33">
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-0.0389485184294415</v>
+        <v>-0.02103403285252858</v>
       </c>
       <c r="F33" t="n">
-        <v>0.28</v>
+        <v>0.3042857142857143</v>
       </c>
     </row>
     <row r="34">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-0.06745416774768256</v>
+        <v>-0.06860549924334534</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3433333333333333</v>
+        <v>0.3383333333333333</v>
       </c>
     </row>
     <row r="35">

--- a/Analysis/Prompt_Ablation/prompt_ablation_summary_by_decision_type.xlsx
+++ b/Analysis/Prompt_Ablation/prompt_ablation_summary_by_decision_type.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,7 +797,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>-0.1486143379339142</v>
+        <v>-0.0007683585346721254</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2769230769230769</v>
+        <v>0.2564102564102564</v>
       </c>
     </row>
     <row r="15">
@@ -825,7 +825,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.1399612755650536</v>
+        <v>0.04928652421780448</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3757142857142857</v>
+        <v>0.2952380952380952</v>
       </c>
     </row>
     <row r="16">
@@ -853,7 +853,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.1678591267774902</v>
+        <v>0.5547231671429942</v>
       </c>
       <c r="F16" t="n">
-        <v>0.38</v>
+        <v>0.5222222222222223</v>
       </c>
     </row>
     <row r="17">
@@ -881,7 +881,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>-0.154903013946784</v>
+        <v>0.07654726848319041</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2817337461300309</v>
+        <v>0.3041237113402062</v>
       </c>
     </row>
     <row r="18">
@@ -909,7 +909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.1037820586478444</v>
+        <v>-0.05341512820896899</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.1857142857142857</v>
       </c>
     </row>
     <row r="19">
@@ -937,7 +937,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.1814780454059473</v>
+        <v>0.6685185185185186</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3434343434343434</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="20">
@@ -965,7 +965,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>-0.1461020407618289</v>
+        <v>0.002477760244073779</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2338461538461538</v>
+        <v>0.2769230769230769</v>
       </c>
     </row>
     <row r="21">
@@ -993,7 +993,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.02958770037436749</v>
+        <v>-0.229838030112909</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3175965665236051</v>
+        <v>0.1333333333333333</v>
       </c>
     </row>
     <row r="22">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.4464674031262856</v>
+        <v>0.6757388508991969</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5716666666666667</v>
+        <v>0.7166666666666667</v>
       </c>
     </row>
     <row r="23">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>-0.1645635792233674</v>
+        <v>-0.001709401709401736</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2676923076923077</v>
+        <v>0.2717948717948718</v>
       </c>
     </row>
     <row r="24">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.04721078597452665</v>
+        <v>0.035794460725741</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3342857142857143</v>
+        <v>0.2904761904761905</v>
       </c>
     </row>
     <row r="25">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.1214655432719637</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="F25" t="n">
-        <v>0.36</v>
+        <v>0.5055555555555555</v>
       </c>
     </row>
     <row r="26">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>-0.1470779937686126</v>
+        <v>-0.1486143379339142</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.2769230769230769</v>
       </c>
     </row>
     <row r="27">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-0.006907822152024003</v>
+        <v>0.1399612755650536</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3161764705882353</v>
+        <v>0.3757142857142857</v>
       </c>
     </row>
     <row r="28">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>-0.0006226115126125598</v>
+        <v>0.1678591267774902</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="29">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-0.06871122668471366</v>
+        <v>-0.154903013946784</v>
       </c>
       <c r="F29" t="n">
-        <v>0.270440251572327</v>
+        <v>0.2817337461300309</v>
       </c>
     </row>
     <row r="30">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-0.06481000976877792</v>
+        <v>0.1037820586478444</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2</v>
+        <v>0.3571428571428572</v>
       </c>
     </row>
     <row r="31">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.4555947722767508</v>
+        <v>0.1814780454059473</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5616438356164384</v>
+        <v>0.3434343434343434</v>
       </c>
     </row>
     <row r="32">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.1576265944969524</v>
+        <v>-0.1461020407618289</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4738461538461539</v>
+        <v>0.2338461538461538</v>
       </c>
     </row>
     <row r="33">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-0.02103403285252858</v>
+        <v>0.02958770037436749</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3042857142857143</v>
+        <v>0.3175965665236051</v>
       </c>
     </row>
     <row r="34">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-0.06860549924334534</v>
+        <v>0.4464674031262856</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3383333333333333</v>
+        <v>0.5716666666666667</v>
       </c>
     </row>
     <row r="35">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-0.1015384615384616</v>
+        <v>-0.1645635792233674</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2215384615384615</v>
+        <v>0.2676923076923077</v>
       </c>
     </row>
     <row r="36">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.04318037187456231</v>
+        <v>0.04721078597452665</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3457142857142857</v>
+        <v>0.3342857142857143</v>
       </c>
     </row>
     <row r="37">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.1130549123215339</v>
+        <v>0.1214655432719637</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4266666666666667</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="38">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.3593547905339141</v>
+        <v>-0.1470779937686126</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6861538461538461</v>
+        <v>0.1851851851851852</v>
       </c>
     </row>
     <row r="39">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.04046690489838687</v>
+        <v>-0.006907822152024003</v>
       </c>
       <c r="F39" t="n">
-        <v>0.38</v>
+        <v>0.3161764705882353</v>
       </c>
     </row>
     <row r="40">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.5522165708851875</v>
+        <v>-0.0006226115126125598</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6066666666666667</v>
+        <v>0.3666666666666666</v>
       </c>
     </row>
     <row r="41">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.1033430964431926</v>
+        <v>-0.06871122668471366</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3580246913580247</v>
+        <v>0.270440251572327</v>
       </c>
     </row>
     <row r="42">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-0.2019047619047619</v>
+        <v>-0.06481000976877792</v>
       </c>
       <c r="F42" t="n">
-        <v>0.09714285714285714</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="43">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1618,26 +1618,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.7070538546981662</v>
+        <v>0.4555947722767508</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5616438356164384</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>no_anchors</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1646,26 +1646,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.3341517527909054</v>
+        <v>0.1576265944969524</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5969230769230769</v>
+        <v>0.4738461538461539</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>no_anchors</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1674,26 +1674,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-0.05267089608355515</v>
+        <v>-0.02103403285252858</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2542857142857143</v>
+        <v>0.3042857142857143</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>no_anchors</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1702,26 +1702,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.4971043076815535</v>
+        <v>-0.06860549924334534</v>
       </c>
       <c r="F46" t="n">
-        <v>0.61</v>
+        <v>0.3383333333333333</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1730,26 +1730,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-0.00205128205128206</v>
+        <v>-0.1015384615384616</v>
       </c>
       <c r="F47" t="n">
-        <v>0.3169230769230769</v>
+        <v>0.2215384615384615</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1758,26 +1758,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.2353343052518416</v>
+        <v>0.04318037187456231</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.3457142857142857</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1786,16 +1786,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.5791638319043511</v>
+        <v>0.1130549123215339</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.4266666666666667</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>control</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1814,16 +1814,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-0.1560590065082022</v>
+        <v>0.3593547905339141</v>
       </c>
       <c r="F50" t="n">
-        <v>0.240625</v>
+        <v>0.6861538461538461</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>control</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1842,16 +1842,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.1832829808660625</v>
+        <v>0.04046690489838687</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4457831325301205</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>control</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1870,16 +1870,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.6185952976439373</v>
+        <v>0.5522165708851875</v>
       </c>
       <c r="F52" t="n">
-        <v>0.656140350877193</v>
+        <v>0.6066666666666667</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1898,16 +1898,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>-0.01128205128205129</v>
+        <v>0.1033430964431926</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3538461538461539</v>
+        <v>0.3580246913580247</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1926,16 +1926,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.2783309035370627</v>
+        <v>-0.2019047619047619</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5342857142857143</v>
+        <v>0.09714285714285714</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1954,16 +1954,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.5360549886030925</v>
+        <v>0.7070538546981662</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1982,16 +1982,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.1789225535823417</v>
+        <v>0.3341517527909054</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5292307692307693</v>
+        <v>0.5969230769230769</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2010,16 +2010,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.1103951640671304</v>
+        <v>-0.05267089608355515</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3628571428571429</v>
+        <v>0.2542857142857143</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>control</t>
+          <t>scale_0_10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2038,16 +2038,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.3475179256106593</v>
+        <v>0.4971043076815535</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5433333333333333</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>control</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2066,16 +2066,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.05087396064072343</v>
+        <v>0.339685461265806</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3919753086419753</v>
+        <v>0.558974358974359</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>control</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2094,16 +2094,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>-0.09918631250691265</v>
+        <v>-0.0515071265758463</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1695402298850575</v>
+        <v>0.2047619047619048</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cot_scaffold</t>
+          <t>control</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2122,16 +2122,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.6924803591470259</v>
+        <v>0.7496258499465421</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6767676767676768</v>
+        <v>0.7055555555555556</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2150,16 +2150,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.1999469848028287</v>
+        <v>0.1527625038735461</v>
       </c>
       <c r="F62" t="n">
-        <v>0.5107692307692308</v>
+        <v>0.4145077720207254</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>scale_0_10</t>
+          <t>cot_scaffold</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2178,37 +2178,625 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.02994581594741723</v>
+        <v>-0.1206349206349206</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3485714285714286</v>
+        <v>0.1380952380952381</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Shower</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.7699962203169125</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>scale_0_10</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>AE</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Appliance</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.1756048814928991</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.4329896907216495</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>scale_0_10</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>-0.1084896336957929</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.1476190476190476</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>scale_0_10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Shower</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.7481481481481482</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Appliance</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>-0.00205128205128206</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.3169230769230769</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.2353343052518416</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Shower</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.5791638319043511</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Appliance</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>-0.1560590065082022</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.240625</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.1832829808660625</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.4457831325301205</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Shower</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.6185952976439373</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.656140350877193</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>scale_0_10</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Appliance</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>-0.01128205128205129</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.3538461538461539</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>scale_0_10</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.2783309035370627</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.5342857142857143</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>scale_0_10</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Shower</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.5360549886030925</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
         <is>
           <t>qwen</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Appliance</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.1789225535823417</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.5292307692307693</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.1103951640671304</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.3628571428571429</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
         <is>
           <t>Shower</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="E79" t="n">
+        <v>0.3475179256106593</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.5433333333333333</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Appliance</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.05087396064072343</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.3919753086419753</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>-0.09918631250691265</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.1695402298850575</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cot_scaffold</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Shower</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.6924803591470259</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.6767676767676768</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>scale_0_10</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Appliance</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.1999469848028287</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.5107692307692308</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>scale_0_10</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.02994581594741723</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.3485714285714286</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>scale_0_10</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Shower</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
         <v>0.07850170085738942</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F85" t="n">
         <v>0.3633333333333333</v>
       </c>
     </row>
